--- a/Config/Datas/Tables/s_升级池_UpgradePoolConfig.xlsx
+++ b/Config/Datas/Tables/s_升级池_UpgradePoolConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbUpgradePool" sheetId="1" r:id="Rcb97799b066b47c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbUpgradePool" sheetId="1" r:id="R95c68ac9bd424ab6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +13,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="6">
+  <x:fonts count="7">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -46,8 +46,14 @@
       <x:color rgb="FF334E68"/>
       <x:name val="Microsoft YaHei"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="14">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -74,8 +80,48 @@
         <x:fgColor rgb="FFF5F8FB"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4472C4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E2F3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4472C4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E2F3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="2">
+  <x:borders count="3">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -91,11 +137,25 @@
         <x:color rgb="FFD7E0E8"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFB8C4D6"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFB8C4D6"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFB8C4D6"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFB8C4D6"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="14">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -132,6 +192,57 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -337,71 +448,134 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="8" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="8" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="11" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="30" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="12" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="27" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="25" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="72" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="72" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="7" t="str">
+      <x:c r="A1" s="24" t="str">
         <x:v>##</x:v>
       </x:c>
-      <x:c r="B1" s="7" t="str">
+      <x:c r="B1" s="24" t="str">
         <x:v>id</x:v>
       </x:c>
-      <x:c r="C1" s="7" t="str">
+      <x:c r="C1" s="24" t="str">
         <x:v>drawCount</x:v>
       </x:c>
-      <x:c r="D1" s="7" t="str">
-        <x:v>optionIds</x:v>
-      </x:c>
+      <x:c r="D1" s="24" t="str">
+        <x:v>exhaustionPolicy</x:v>
+      </x:c>
+      <x:c r="E1" s="24" t="str">
+        <x:v>fallbackPoolId</x:v>
+      </x:c>
+      <x:c r="F1" s="24" t="str">
+        <x:v>entries</x:v>
+      </x:c>
+      <x:c r="G1"/>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="9" t="str">
+      <x:c r="A2" s="26" t="str">
         <x:v>##type</x:v>
       </x:c>
-      <x:c r="B2" s="9" t="str">
+      <x:c r="B2" s="26" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="C2" s="9" t="str">
+      <x:c r="C2" s="26" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="D2" s="9" t="str">
-        <x:v>(list#sep=;),int#ref=TbUpgradeOption</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="22" customHeight="1">
-      <x:c r="A3" s="11" t="str">
+      <x:c r="D2" s="26" t="str">
+        <x:v>EUpgradeExhaustionPolicy</x:v>
+      </x:c>
+      <x:c r="E2" s="26" t="str">
+        <x:v>int?#ref=TbUpgradePool</x:v>
+      </x:c>
+      <x:c r="F2" s="26" t="str">
+        <x:v>(list#sep=;),UpgradePoolEntry</x:v>
+      </x:c>
+      <x:c r="G2"/>
+    </x:row>
+    <x:row r="3" ht="24" customHeight="1">
+      <x:c r="A3" s="28" t="str">
         <x:v>##var</x:v>
       </x:c>
-      <x:c r="B3" s="11"/>
-      <x:c r="C3" s="11"/>
-      <x:c r="D3" s="11"/>
-    </x:row>
-    <x:row r="4" ht="54" customHeight="1">
-      <x:c r="A4" s="13" t="str">
+      <x:c r="B3" s="28"/>
+      <x:c r="C3" s="28"/>
+      <x:c r="D3" s="28"/>
+      <x:c r="E3" s="28"/>
+      <x:c r="F3" s="28"/>
+      <x:c r="G3"/>
+    </x:row>
+    <x:row r="4" ht="36" customHeight="1">
+      <x:c r="A4" s="30" t="str">
         <x:v>##</x:v>
       </x:c>
-      <x:c r="B4" s="13" t="str">
+      <x:c r="B4" s="30" t="str">
         <x:v>升级池ID</x:v>
       </x:c>
-      <x:c r="C4" s="13" t="str">
-        <x:v>每次无放回候选数量</x:v>
-      </x:c>
-      <x:c r="D4" s="13" t="str">
-        <x:v>可用升级选项</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="5"/>
-      <x:c r="B5" s="5" t="n">
+      <x:c r="C4" s="30" t="str">
+        <x:v>每次最多展示数量</x:v>
+      </x:c>
+      <x:c r="D4" s="30" t="str">
+        <x:v>候选不足时的处理策略</x:v>
+      </x:c>
+      <x:c r="E4" s="30" t="str">
+        <x:v>后备池；仅FallbackPool填写</x:v>
+      </x:c>
+      <x:c r="F4" s="30" t="str">
+        <x:v>选项ID:池内权重</x:v>
+      </x:c>
+      <x:c r="G4"/>
+    </x:row>
+    <x:row r="5" ht="54" customHeight="1">
+      <x:c r="A5" s="14"/>
+      <x:c r="B5" s="14" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="5" t="n">
+      <x:c r="C5" s="14" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D5" s="5" t="str">
-        <x:v>40001;40002;40003;40004;40005;40006;40007;40008;40009</x:v>
+      <x:c r="D5" s="14" t="str">
+        <x:v>ReduceOfferCount</x:v>
+      </x:c>
+      <x:c r="E5" s="14"/>
+      <x:c r="F5" s="14" t="str">
+        <x:v>40001:100;40002:100;40003:100;40004:100;40005:100;40006:100;40007:100;40008:100;40009:80</x:v>
+      </x:c>
+      <x:c r="G5"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6"/>
+      <x:c r="B6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C6" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D6" t="str">
+        <x:v>ReduceOfferCount</x:v>
+      </x:c>
+      <x:c r="E6"/>
+      <x:c r="F6" t="str">
+        <x:v>41001:100;41002:100;41003:100;41004:100;41005:100;41006:100;41007:100;41008:100;41009:100;41010:100;41011:100;41012:100;40009:40</x:v>
+      </x:c>
+      <x:c r="G6"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="B7" t="n">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" t="str">
+        <x:v>ReduceOfferCount</x:v>
+      </x:c>
+      <x:c r="F7" t="str">
+        <x:v>41003:100;41004:100;41005:100;41007:100;41008:100;41009:100;41010:100;41011:100;41012:100;40009:40</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Config/Datas/Tables/s_升级池_UpgradePoolConfig.xlsx
+++ b/Config/Datas/Tables/s_升级池_UpgradePoolConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbUpgradePool" sheetId="1" r:id="R95c68ac9bd424ab6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbUpgradePool" sheetId="1" r:id="R5c18839f95884464"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -560,7 +560,7 @@
       </x:c>
       <x:c r="E6"/>
       <x:c r="F6" t="str">
-        <x:v>41001:100;41002:100;41003:100;41004:100;41005:100;41006:100;41007:100;41008:100;41009:100;41010:100;41011:100;41012:100;40009:40</x:v>
+        <x:v>41001:100;41002:100;41003:100;41004:100;41005:100;41006:100;41007:100;41008:100;41009:100;41010:100;41011:100;41012:100;40009:40;42001:100</x:v>
       </x:c>
       <x:c r="G6"/>
     </x:row>
@@ -575,7 +575,7 @@
         <x:v>ReduceOfferCount</x:v>
       </x:c>
       <x:c r="F7" t="str">
-        <x:v>41003:100;41004:100;41005:100;41007:100;41008:100;41009:100;41010:100;41011:100;41012:100;40009:40</x:v>
+        <x:v>41003:100;41004:100;41005:100;41007:100;41008:100;41009:100;41010:100;41011:100;41012:100;40009:40;42002:100</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
